--- a/datatables/httk-benchmarks.xlsx
+++ b/datatables/httk-benchmarks.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jwambaug\git\httk-dev\datatables\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\WambaughJohn\git\httk-new\datatables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12ECD942-4BD4-4BA7-98E4-39DD13801945}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33F2E2EB-541E-47E6-9CF6-09EA2A42C684}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1215" yWindow="1365" windowWidth="27585" windowHeight="11820" xr2:uid="{C208547E-DF7E-4D1E-AF51-B4A727438EC0}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{C208547E-DF7E-4D1E-AF51-B4A727438EC0}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="62">
   <si>
     <t>2.2.2</t>
   </si>
@@ -206,6 +206,24 @@
   </si>
   <si>
     <t>Updated CvTdb fits (invivoPKfit)</t>
+  </si>
+  <si>
+    <t>2.7.4</t>
+  </si>
+  <si>
+    <t>Added new predictions for Dawson QSPR</t>
+  </si>
+  <si>
+    <t>2.7.2</t>
+  </si>
+  <si>
+    <t>2.7.3</t>
+  </si>
+  <si>
+    <t>Stability and message fixes</t>
+  </si>
+  <si>
+    <t>Stability fixes for dermal and 3comp2 model</t>
   </si>
 </sst>
 </file>
@@ -428,9 +446,9 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$A$2:$A$31</c:f>
+              <c:f>Sheet1!$A$2:$A$34</c:f>
               <c:strCache>
-                <c:ptCount val="30"/>
+                <c:ptCount val="33"/>
                 <c:pt idx="0">
                   <c:v>1.1</c:v>
                 </c:pt>
@@ -520,16 +538,25 @@
                 </c:pt>
                 <c:pt idx="29">
                   <c:v>2.7.1</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>2.7.2</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>2.7.3</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>2.7.4</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$F$2:$F$31</c:f>
+              <c:f>Sheet1!$F$2:$F$34</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="30"/>
+                <c:ptCount val="33"/>
                 <c:pt idx="0">
                   <c:v>0.52929999999999999</c:v>
                 </c:pt>
@@ -619,6 +646,15 @@
                 </c:pt>
                 <c:pt idx="29">
                   <c:v>0.93500000000000005</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>0.93500000000000005</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>0.93500000000000005</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>0.93479999999999996</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -925,6 +961,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -932,7 +969,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -1057,9 +1093,9 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$A$2:$A$31</c:f>
+              <c:f>Sheet1!$A$2:$A$34</c:f>
               <c:strCache>
-                <c:ptCount val="30"/>
+                <c:ptCount val="33"/>
                 <c:pt idx="0">
                   <c:v>1.1</c:v>
                 </c:pt>
@@ -1149,16 +1185,25 @@
                 </c:pt>
                 <c:pt idx="29">
                   <c:v>2.7.1</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>2.7.2</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>2.7.3</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>2.7.4</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$J$2:$J$31</c:f>
+              <c:f>Sheet1!$J$2:$J$34</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="30"/>
+                <c:ptCount val="33"/>
                 <c:pt idx="0">
                   <c:v>1.869</c:v>
                 </c:pt>
@@ -1247,6 +1292,15 @@
                   <c:v>2.3740000000000001</c:v>
                 </c:pt>
                 <c:pt idx="29">
+                  <c:v>2.1840000000000002</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>2.1840000000000002</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>2.1840000000000002</c:v>
+                </c:pt>
+                <c:pt idx="32">
                   <c:v>2.1840000000000002</c:v>
                 </c:pt>
               </c:numCache>
@@ -1560,6 +1614,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -1567,7 +1622,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -2792,8 +2846,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{3DD92D36-BFF3-413F-93A1-8D3D8569B858}" name="Table1" displayName="Table1" ref="A1:R31" totalsRowShown="0" headerRowDxfId="19" dataDxfId="18">
-  <autoFilter ref="A1:R31" xr:uid="{3DD92D36-BFF3-413F-93A1-8D3D8569B858}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{3DD92D36-BFF3-413F-93A1-8D3D8569B858}" name="Table1" displayName="Table1" ref="A1:R34" totalsRowShown="0" headerRowDxfId="19" dataDxfId="18">
+  <autoFilter ref="A1:R34" xr:uid="{3DD92D36-BFF3-413F-93A1-8D3D8569B858}"/>
   <tableColumns count="18">
     <tableColumn id="1" xr3:uid="{478C9B49-D67B-44BA-B8BF-86E093E572FE}" name="Version" dataDxfId="17"/>
     <tableColumn id="13" xr3:uid="{1CCFB984-6FEC-43E4-BB73-000E230E2655}" name="N.steadystate" dataDxfId="16"/>
@@ -3115,19 +3169,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7AA7C988-D5EA-4528-8554-7DA2671EBD43}">
-  <dimension ref="A1:R31"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:R34"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="5" width="10.42578125" customWidth="1"/>
-    <col min="6" max="6" width="16.85546875" customWidth="1"/>
-    <col min="7" max="7" width="12.85546875" customWidth="1"/>
-    <col min="8" max="8" width="13.85546875" customWidth="1"/>
-    <col min="9" max="10" width="9.7109375" customWidth="1"/>
-    <col min="11" max="17" width="6.7109375" customWidth="1"/>
-    <col min="18" max="18" width="39.42578125" customWidth="1"/>
+    <col min="1" max="5" width="10.44140625" customWidth="1"/>
+    <col min="6" max="6" width="16.88671875" customWidth="1"/>
+    <col min="7" max="7" width="12.88671875" customWidth="1"/>
+    <col min="8" max="8" width="13.88671875" customWidth="1"/>
+    <col min="9" max="10" width="9.6640625" customWidth="1"/>
+    <col min="11" max="17" width="6.6640625" customWidth="1"/>
+    <col min="18" max="18" width="39.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>15</v>
       </c>
@@ -3183,7 +3237,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>1.1000000000000001</v>
       </c>
@@ -3233,7 +3287,7 @@
       <c r="Q2" s="1"/>
       <c r="R2" s="1"/>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>1.2</v>
       </c>
@@ -3283,7 +3337,7 @@
       <c r="Q3" s="1"/>
       <c r="R3" s="1"/>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>1.3</v>
       </c>
@@ -3337,7 +3391,7 @@
       </c>
       <c r="R4" s="1"/>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>1.4</v>
       </c>
@@ -3391,7 +3445,7 @@
       </c>
       <c r="R5" s="1"/>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>1.5</v>
       </c>
@@ -3447,7 +3501,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>1.6</v>
       </c>
@@ -3503,7 +3557,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>1.7</v>
       </c>
@@ -3557,7 +3611,7 @@
       </c>
       <c r="R8" s="1"/>
     </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>1.8</v>
       </c>
@@ -3611,7 +3665,7 @@
       </c>
       <c r="R9" s="1"/>
     </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <v>1.9</v>
       </c>
@@ -3665,7 +3719,7 @@
       </c>
       <c r="R10" s="1"/>
     </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>16</v>
       </c>
@@ -3721,7 +3775,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
         <v>4</v>
       </c>
@@ -3775,7 +3829,7 @@
       </c>
       <c r="R12" s="1"/>
     </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
         <v>8</v>
       </c>
@@ -3831,7 +3885,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
         <v>17</v>
       </c>
@@ -3885,7 +3939,7 @@
       </c>
       <c r="R14" s="1"/>
     </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
         <v>7</v>
       </c>
@@ -3941,7 +3995,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
         <v>14</v>
       </c>
@@ -3995,7 +4049,7 @@
       </c>
       <c r="R16" s="1"/>
     </row>
-    <row r="17" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
         <v>13</v>
       </c>
@@ -4049,7 +4103,7 @@
       </c>
       <c r="R17" s="1"/>
     </row>
-    <row r="18" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
         <v>12</v>
       </c>
@@ -4103,7 +4157,7 @@
       </c>
       <c r="R18" s="1"/>
     </row>
-    <row r="19" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
         <v>11</v>
       </c>
@@ -4157,7 +4211,7 @@
       </c>
       <c r="R19" s="1"/>
     </row>
-    <row r="20" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
         <v>10</v>
       </c>
@@ -4213,7 +4267,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="21" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
         <v>9</v>
       </c>
@@ -4269,7 +4323,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="22" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
         <v>3</v>
       </c>
@@ -4323,7 +4377,7 @@
       </c>
       <c r="R22" s="1"/>
     </row>
-    <row r="23" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
         <v>0</v>
       </c>
@@ -4379,7 +4433,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="24" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
         <v>41</v>
       </c>
@@ -4435,7 +4489,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="25" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
         <v>43</v>
       </c>
@@ -4489,7 +4543,7 @@
       </c>
       <c r="R25" s="1"/>
     </row>
-    <row r="26" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
         <v>44</v>
       </c>
@@ -4545,7 +4599,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="27" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
         <v>46</v>
       </c>
@@ -4601,7 +4655,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="28" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
         <v>48</v>
       </c>
@@ -4657,7 +4711,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="29" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
         <v>50</v>
       </c>
@@ -4713,7 +4767,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="30" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
         <v>52</v>
       </c>
@@ -4769,7 +4823,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="31" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
         <v>54</v>
       </c>
@@ -4823,6 +4877,174 @@
       </c>
       <c r="R31" s="1" t="s">
         <v>55</v>
+      </c>
+    </row>
+    <row r="32" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A32" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B32" s="1">
+        <v>1026</v>
+      </c>
+      <c r="C32" s="1">
+        <v>0.99980000000000002</v>
+      </c>
+      <c r="D32" s="1">
+        <v>1</v>
+      </c>
+      <c r="E32" s="1">
+        <v>0.99990000000000001</v>
+      </c>
+      <c r="F32" s="1">
+        <v>0.93500000000000005</v>
+      </c>
+      <c r="G32" s="1">
+        <v>352</v>
+      </c>
+      <c r="H32" s="1">
+        <v>0.27110000000000001</v>
+      </c>
+      <c r="I32" s="1">
+        <v>352</v>
+      </c>
+      <c r="J32" s="1">
+        <v>2.1840000000000002</v>
+      </c>
+      <c r="K32" s="1">
+        <v>100</v>
+      </c>
+      <c r="L32" s="1">
+        <v>1.2929999999999999</v>
+      </c>
+      <c r="M32" s="1">
+        <v>112</v>
+      </c>
+      <c r="N32" s="1">
+        <v>1.2130000000000001</v>
+      </c>
+      <c r="O32" s="1">
+        <v>156</v>
+      </c>
+      <c r="P32" s="1">
+        <v>0.629</v>
+      </c>
+      <c r="Q32" s="1">
+        <v>863</v>
+      </c>
+      <c r="R32" s="1" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="33" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A33" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B33" s="1">
+        <v>1026</v>
+      </c>
+      <c r="C33" s="1">
+        <v>0.99980000000000002</v>
+      </c>
+      <c r="D33" s="1">
+        <v>1</v>
+      </c>
+      <c r="E33" s="1">
+        <v>0.99990000000000001</v>
+      </c>
+      <c r="F33" s="1">
+        <v>0.93500000000000005</v>
+      </c>
+      <c r="G33" s="1">
+        <v>352</v>
+      </c>
+      <c r="H33" s="1">
+        <v>0.27110000000000001</v>
+      </c>
+      <c r="I33" s="1">
+        <v>352</v>
+      </c>
+      <c r="J33" s="1">
+        <v>2.1840000000000002</v>
+      </c>
+      <c r="K33" s="1">
+        <v>100</v>
+      </c>
+      <c r="L33" s="1">
+        <v>1.2929999999999999</v>
+      </c>
+      <c r="M33" s="1">
+        <v>112</v>
+      </c>
+      <c r="N33" s="1">
+        <v>1.2130000000000001</v>
+      </c>
+      <c r="O33" s="1">
+        <v>156</v>
+      </c>
+      <c r="P33" s="1">
+        <v>0.629</v>
+      </c>
+      <c r="Q33" s="1">
+        <v>863</v>
+      </c>
+      <c r="R33" s="1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="34" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A34" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B34" s="1">
+        <v>1026</v>
+      </c>
+      <c r="C34" s="1">
+        <v>0.99980000000000002</v>
+      </c>
+      <c r="D34" s="1">
+        <v>1</v>
+      </c>
+      <c r="E34" s="1">
+        <v>0.99990000000000001</v>
+      </c>
+      <c r="F34" s="1">
+        <v>0.93479999999999996</v>
+      </c>
+      <c r="G34" s="1">
+        <v>352</v>
+      </c>
+      <c r="H34" s="1">
+        <v>0.2712</v>
+      </c>
+      <c r="I34" s="1">
+        <v>352</v>
+      </c>
+      <c r="J34" s="1">
+        <v>2.1840000000000002</v>
+      </c>
+      <c r="K34" s="1">
+        <v>100</v>
+      </c>
+      <c r="L34" s="1">
+        <v>1.2929999999999999</v>
+      </c>
+      <c r="M34" s="1">
+        <v>112</v>
+      </c>
+      <c r="N34" s="1">
+        <v>1.2130000000000001</v>
+      </c>
+      <c r="O34" s="1">
+        <v>156</v>
+      </c>
+      <c r="P34" s="1">
+        <v>0.629</v>
+      </c>
+      <c r="Q34" s="1">
+        <v>863</v>
+      </c>
+      <c r="R34" s="1" t="s">
+        <v>57</v>
       </c>
     </row>
   </sheetData>
